--- a/data/trans_orig/P05A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>534222</t>
+          <t>529407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>595627</t>
+          <t>594751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>648725</t>
+          <t>648278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>721772</t>
+          <t>719730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1202031</t>
+          <t>1202958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1297057</t>
+          <t>1295247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>335194</t>
+          <t>334021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395022</t>
+          <t>398293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415674</t>
+          <t>418609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485381</t>
+          <t>485523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765671</t>
+          <t>772140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>859181</t>
+          <t>860087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86130</t>
+          <t>86354</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124236</t>
+          <t>126213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152072</t>
+          <t>153132</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203418</t>
+          <t>202268</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>252794</t>
+          <t>251887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>315121</t>
+          <t>314742</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>834436</t>
+          <t>832477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>915044</t>
+          <t>921080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>738697</t>
+          <t>733468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>818162</t>
+          <t>815284</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1597731</t>
+          <t>1597668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1716284</t>
+          <t>1713298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>622930</t>
+          <t>622060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>698865</t>
+          <t>700461</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>550492</t>
+          <t>552231</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>629711</t>
+          <t>631047</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1198231</t>
+          <t>1196674</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1311785</t>
+          <t>1311088</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131744</t>
+          <t>133958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182587</t>
+          <t>183431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188153</t>
+          <t>192258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241653</t>
+          <t>246414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>334810</t>
+          <t>335856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>408817</t>
+          <t>411254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>268836</t>
+          <t>266255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316997</t>
+          <t>315341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>213845</t>
+          <t>211080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>258266</t>
+          <t>257123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>492141</t>
+          <t>495200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>557359</t>
+          <t>560545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170297</t>
+          <t>168069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214856</t>
+          <t>215626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156854</t>
+          <t>158332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200899</t>
+          <t>201309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342888</t>
+          <t>338212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>406021</t>
+          <t>401086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49968</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82898</t>
+          <t>82638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>49805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80193</t>
+          <t>80059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108109</t>
+          <t>108631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151258</t>
+          <t>150203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1671918</t>
+          <t>1671606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1787667</t>
+          <t>1788804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1640577</t>
+          <t>1638876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1756357</t>
+          <t>1753476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3356520</t>
+          <t>3340558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3518119</t>
+          <t>3503987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1164232</t>
+          <t>1162947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1277100</t>
+          <t>1272086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1168636</t>
+          <t>1168849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1280920</t>
+          <t>1275453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2359015</t>
+          <t>2360398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2512847</t>
+          <t>2519056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>296613</t>
+          <t>293495</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>362488</t>
+          <t>362341</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>414955</t>
+          <t>420122</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>495318</t>
+          <t>495299</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>723227</t>
+          <t>734002</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>836954</t>
+          <t>836581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>662342</t>
+          <t>660811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>719514</t>
+          <t>718048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>910980</t>
+          <t>909915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>976716</t>
+          <t>981176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1592787</t>
+          <t>1593424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1684184</t>
+          <t>1679507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194207</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246206</t>
+          <t>248019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273465</t>
+          <t>271811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333273</t>
+          <t>333577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480822</t>
+          <t>478004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565092</t>
+          <t>562776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48714</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80647</t>
+          <t>79290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71215</t>
+          <t>72158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>108590</t>
+          <t>110206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>130070</t>
+          <t>129659</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>178079</t>
+          <t>178191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1298295</t>
+          <t>1299007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1379437</t>
+          <t>1379792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1181357</t>
+          <t>1186953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1264704</t>
+          <t>1265221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2499821</t>
+          <t>2503982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2617598</t>
+          <t>2618207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>465417</t>
+          <t>468586</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>543321</t>
+          <t>545651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>372821</t>
+          <t>375615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447251</t>
+          <t>447811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>865412</t>
+          <t>866185</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>974490</t>
+          <t>970178</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94995</t>
+          <t>95479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136129</t>
+          <t>138918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93832</t>
+          <t>93638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136653</t>
+          <t>138410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201599</t>
+          <t>202093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>265578</t>
+          <t>261522</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281804</t>
+          <t>280145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>327119</t>
+          <t>326779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>298107</t>
+          <t>298596</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>339736</t>
+          <t>339638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>595276</t>
+          <t>592801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>655375</t>
+          <t>655357</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117300</t>
+          <t>118982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160844</t>
+          <t>161628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88912</t>
+          <t>87919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>125814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220971</t>
+          <t>219853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>276964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>25609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50758</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>22607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53094</t>
+          <t>53729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86424</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2282865</t>
+          <t>2284465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2391583</t>
+          <t>2397552</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2432861</t>
+          <t>2435957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2546109</t>
+          <t>2546766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4748752</t>
+          <t>4745665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4909402</t>
+          <t>4909391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>809433</t>
+          <t>807401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>916770</t>
+          <t>913846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>771278</t>
+          <t>772434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>875591</t>
+          <t>874933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1604299</t>
+          <t>1611733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1750958</t>
+          <t>1759295</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187693</t>
+          <t>186014</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>245574</t>
+          <t>249647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,82 +4397,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>235845</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>204989</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>266137</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>451143</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>409203</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>500300</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>7,19%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>235845</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>206160</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>267885</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>451143</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>410612</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>495462</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>504186</t>
+          <t>501895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>553014</t>
+          <t>552436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>693587</t>
+          <t>692179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>752104</t>
+          <t>752201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1211900</t>
+          <t>1214167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1292437</t>
+          <t>1288916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154439</t>
+          <t>154336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201788</t>
+          <t>200414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181829</t>
+          <t>182101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235141</t>
+          <t>235300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350678</t>
+          <t>353642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>421469</t>
+          <t>424900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35864</t>
+          <t>35389</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61786</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>46081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77366</t>
+          <t>77855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87592</t>
+          <t>86255</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131270</t>
+          <t>129752</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1430990</t>
+          <t>1434920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1512761</t>
+          <t>1518290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1370297</t>
+          <t>1364188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1450740</t>
+          <t>1448023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2821098</t>
+          <t>2823281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2939250</t>
+          <t>2945811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,55%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>463993</t>
+          <t>458702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>541155</t>
+          <t>540326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>414001</t>
+          <t>418364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>492026</t>
+          <t>494496</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>901306</t>
+          <t>899471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008677</t>
+          <t>1012843</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79399</t>
+          <t>78650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120695</t>
+          <t>118685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103773</t>
+          <t>102415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151112</t>
+          <t>146655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194738</t>
+          <t>192771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253589</t>
+          <t>251773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>373669</t>
+          <t>373477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415159</t>
+          <t>415953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>361618</t>
+          <t>362315</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>404965</t>
+          <t>403867</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>745494</t>
+          <t>744967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>806353</t>
+          <t>807628</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105269</t>
+          <t>104935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144503</t>
+          <t>145399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100606</t>
+          <t>102193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139546</t>
+          <t>139423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216702</t>
+          <t>215516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269329</t>
+          <t>273929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>40343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60690</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56500</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91981</t>
+          <t>93341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2350654</t>
+          <t>2344480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2454776</t>
+          <t>2455550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2461914</t>
+          <t>2452028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2563979</t>
+          <t>2567929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4842487</t>
+          <t>4838855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4985082</t>
+          <t>4990874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>747511</t>
+          <t>751241</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>848503</t>
+          <t>851063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731941</t>
+          <t>731678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>827755</t>
+          <t>832118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1517132</t>
+          <t>1514447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1651617</t>
+          <t>1660841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>148165</t>
+          <t>147566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202217</t>
+          <t>201012</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204305</t>
+          <t>202616</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>265231</t>
+          <t>261689</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>364867</t>
+          <t>365765</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>448423</t>
+          <t>446909</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>388019</t>
+          <t>387400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>421654</t>
+          <t>421357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>578372</t>
+          <t>577658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>613121</t>
+          <t>613731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>979023</t>
+          <t>974755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1025639</t>
+          <t>1026223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>56327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84915</t>
+          <t>83350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98170</t>
+          <t>97219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128989</t>
+          <t>127836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161876</t>
+          <t>161441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201752</t>
+          <t>203936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>27294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50088</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>57140</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70282</t>
+          <t>68465</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100719</t>
+          <t>100639</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1779083</t>
+          <t>1775671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1992490</t>
+          <t>1989773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1140908</t>
+          <t>1169138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1776269</t>
+          <t>1773128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2900873</t>
+          <t>2907918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3648002</t>
+          <t>3650099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>240015</t>
+          <t>239341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>408168</t>
+          <t>411908</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>348222</t>
+          <t>351112</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1015090</t>
+          <t>992212</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>678737</t>
+          <t>677798</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1454962</t>
+          <t>1430700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>63168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114914</t>
+          <t>115729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76480</t>
+          <t>75790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131829</t>
+          <t>133024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155356</t>
+          <t>157656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233160</t>
+          <t>236173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>437870</t>
+          <t>439032</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>493196</t>
+          <t>492753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>463774</t>
+          <t>463515</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>502814</t>
+          <t>504137</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>913295</t>
+          <t>912847</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>983568</t>
+          <t>983723</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116715</t>
+          <t>115392</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162267</t>
+          <t>159449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107423</t>
+          <t>108675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142301</t>
+          <t>144271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236004</t>
+          <t>237672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295077</t>
+          <t>294635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71636</t>
+          <t>71300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>38097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61804</t>
+          <t>62605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>70831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121680</t>
+          <t>120756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2640628</t>
+          <t>2642690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2885438</t>
+          <t>2888729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2060283</t>
+          <t>2159823</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2851017</t>
+          <t>2855658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4805740</t>
+          <t>4819595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5610281</t>
+          <t>5592956</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441832</t>
+          <t>434909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623721</t>
+          <t>623305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>587961</t>
+          <t>584445</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1432112</t>
+          <t>1334282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1123550</t>
+          <t>1129633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1956236</t>
+          <t>1938707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133273</t>
+          <t>130097</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>209042</t>
+          <t>210330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162978</t>
+          <t>163252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>233157</t>
+          <t>232468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>316463</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>422761</t>
+          <t>420189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>529407</t>
+          <t>532581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>594751</t>
+          <t>594921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>648278</t>
+          <t>648555</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>719730</t>
+          <t>721350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1202958</t>
+          <t>1203256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1295247</t>
+          <t>1298722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>334021</t>
+          <t>330406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398293</t>
+          <t>390858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>418609</t>
+          <t>419224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485523</t>
+          <t>488158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772140</t>
+          <t>767084</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>860087</t>
+          <t>857042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126213</t>
+          <t>124307</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153132</t>
+          <t>153216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>202268</t>
+          <t>201458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251887</t>
+          <t>252892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>314742</t>
+          <t>315773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>832477</t>
+          <t>833357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>921080</t>
+          <t>917140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>733468</t>
+          <t>737780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>815284</t>
+          <t>816249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1597668</t>
+          <t>1593799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1713298</t>
+          <t>1711451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>622060</t>
+          <t>621517</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>700461</t>
+          <t>702788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>552231</t>
+          <t>555274</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>631047</t>
+          <t>630458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1196674</t>
+          <t>1197626</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1311088</t>
+          <t>1309570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133958</t>
+          <t>132355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183431</t>
+          <t>182429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192258</t>
+          <t>187851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246414</t>
+          <t>242158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>335856</t>
+          <t>336633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>411254</t>
+          <t>406637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>266255</t>
+          <t>266996</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315341</t>
+          <t>315358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211080</t>
+          <t>212748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257123</t>
+          <t>257516</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495200</t>
+          <t>494897</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>560545</t>
+          <t>562664</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>168069</t>
+          <t>170607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215626</t>
+          <t>215104</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158332</t>
+          <t>158004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201309</t>
+          <t>200756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338212</t>
+          <t>336796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>401086</t>
+          <t>401520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51066</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82638</t>
+          <t>83266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49805</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80059</t>
+          <t>80624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108631</t>
+          <t>108431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150203</t>
+          <t>150077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1671606</t>
+          <t>1669534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1788804</t>
+          <t>1783761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1638876</t>
+          <t>1638891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1753476</t>
+          <t>1756622</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3340558</t>
+          <t>3349443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3503987</t>
+          <t>3512657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1162947</t>
+          <t>1164147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1272086</t>
+          <t>1273017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1168849</t>
+          <t>1167324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1275453</t>
+          <t>1277303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2360398</t>
+          <t>2353486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2519056</t>
+          <t>2514724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>293495</t>
+          <t>294368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>362341</t>
+          <t>363283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>420122</t>
+          <t>411152</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>495299</t>
+          <t>493231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>734002</t>
+          <t>734417</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>836581</t>
+          <t>837105</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>660811</t>
+          <t>659629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>718048</t>
+          <t>718254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>909915</t>
+          <t>914011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>981176</t>
+          <t>982166</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1593424</t>
+          <t>1592080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1679507</t>
+          <t>1685596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194302</t>
+          <t>193235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248019</t>
+          <t>248684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271811</t>
+          <t>270765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333577</t>
+          <t>330894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>478004</t>
+          <t>476941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562776</t>
+          <t>559769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47921</t>
+          <t>50219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79290</t>
+          <t>80577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72158</t>
+          <t>71081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110206</t>
+          <t>108600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>129659</t>
+          <t>128123</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>178191</t>
+          <t>180974</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1299007</t>
+          <t>1301646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1379792</t>
+          <t>1381788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1186953</t>
+          <t>1186285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1265221</t>
+          <t>1262201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2503982</t>
+          <t>2507788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2618207</t>
+          <t>2625931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>468586</t>
+          <t>466826</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>545651</t>
+          <t>543731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>375615</t>
+          <t>375849</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447811</t>
+          <t>449595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>866185</t>
+          <t>862786</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>970178</t>
+          <t>972017</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95479</t>
+          <t>94675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138918</t>
+          <t>136768</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93638</t>
+          <t>96432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138410</t>
+          <t>138450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202093</t>
+          <t>201382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261522</t>
+          <t>263474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>280145</t>
+          <t>283430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>326779</t>
+          <t>330215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>298596</t>
+          <t>300204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>339638</t>
+          <t>340020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>592801</t>
+          <t>595271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>655357</t>
+          <t>655782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118982</t>
+          <t>119395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161628</t>
+          <t>160074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87919</t>
+          <t>87908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125814</t>
+          <t>125419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>219853</t>
+          <t>217343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276964</t>
+          <t>276332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52199</t>
+          <t>51186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>44946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53729</t>
+          <t>53879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87440</t>
+          <t>87663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2284465</t>
+          <t>2280788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2397552</t>
+          <t>2393656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2435957</t>
+          <t>2434910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2546766</t>
+          <t>2547508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4745665</t>
+          <t>4752480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4909391</t>
+          <t>4908788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>807401</t>
+          <t>807340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>913846</t>
+          <t>913097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>772434</t>
+          <t>765618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>874933</t>
+          <t>874142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1611733</t>
+          <t>1612816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1759295</t>
+          <t>1757637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186014</t>
+          <t>188482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>249647</t>
+          <t>244701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204989</t>
+          <t>205466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266137</t>
+          <t>269323</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>409203</t>
+          <t>411892</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>500300</t>
+          <t>490978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>501895</t>
+          <t>504463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>552436</t>
+          <t>554608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>692179</t>
+          <t>689463</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>752201</t>
+          <t>750791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1214167</t>
+          <t>1220100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1288916</t>
+          <t>1294601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154336</t>
+          <t>154602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200414</t>
+          <t>201040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182101</t>
+          <t>182629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235300</t>
+          <t>237323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>353642</t>
+          <t>350271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>424900</t>
+          <t>418679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63593</t>
+          <t>62286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77855</t>
+          <t>77340</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86255</t>
+          <t>87521</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>129752</t>
+          <t>127871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1434920</t>
+          <t>1435515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1518290</t>
+          <t>1518424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1364188</t>
+          <t>1370167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1448023</t>
+          <t>1449971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2823281</t>
+          <t>2825545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2945811</t>
+          <t>2941137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>458702</t>
+          <t>460660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>540326</t>
+          <t>538160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>418364</t>
+          <t>417792</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>494496</t>
+          <t>491715</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>899471</t>
+          <t>904964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1012843</t>
+          <t>1012233</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78650</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118685</t>
+          <t>118585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102415</t>
+          <t>104842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146655</t>
+          <t>145364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192771</t>
+          <t>191438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251773</t>
+          <t>252966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>373477</t>
+          <t>371824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415953</t>
+          <t>415572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>362315</t>
+          <t>361343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>403867</t>
+          <t>404191</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>744967</t>
+          <t>746394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>807628</t>
+          <t>809894</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104935</t>
+          <t>105517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145399</t>
+          <t>146772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102193</t>
+          <t>100048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139423</t>
+          <t>138443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215516</t>
+          <t>216212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273929</t>
+          <t>275702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40343</t>
+          <t>40335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>33409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61053</t>
+          <t>61736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57662</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93341</t>
+          <t>92717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2344480</t>
+          <t>2348467</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2455550</t>
+          <t>2456267</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2452028</t>
+          <t>2460083</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2567929</t>
+          <t>2568213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4838855</t>
+          <t>4837630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4990874</t>
+          <t>4990922</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>751241</t>
+          <t>749116</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>851063</t>
+          <t>850905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731678</t>
+          <t>729566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>832118</t>
+          <t>827899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1514447</t>
+          <t>1510425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1660841</t>
+          <t>1656340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147566</t>
+          <t>145742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201012</t>
+          <t>199272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202616</t>
+          <t>201934</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>261689</t>
+          <t>264871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>365765</t>
+          <t>361461</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>446909</t>
+          <t>442093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>405420</t>
+          <t>454443</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>387400</t>
+          <t>435207</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>421357</t>
+          <t>471794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>596748</t>
+          <t>645222</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>577658</t>
+          <t>623316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>613731</t>
+          <t>663194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1002168</t>
+          <t>1099666</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>974755</t>
+          <t>1071805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1026223</t>
+          <t>1124584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69591</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>66178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>97070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>112269</t>
+          <t>125455</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97219</t>
+          <t>109400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127836</t>
+          <t>143138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>181860</t>
+          <t>207219</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161441</t>
+          <t>185761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203936</t>
+          <t>229547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>40391</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27294</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>53684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45871</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36190</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57140</t>
+          <t>62670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>83943</t>
+          <t>91076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68465</t>
+          <t>76583</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100639</t>
+          <t>109506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513084</t>
+          <t>576598</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513084</t>
+          <t>576598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513084</t>
+          <t>576598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754888</t>
+          <t>821363</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754888</t>
+          <t>821363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754888</t>
+          <t>821363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1267972</t>
+          <t>1397961</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1267972</t>
+          <t>1397961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1267972</t>
+          <t>1397961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1848153</t>
+          <t>1732107</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1775671</t>
+          <t>1687543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1989773</t>
+          <t>1774800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1595233</t>
+          <t>1670518</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1169138</t>
+          <t>1627380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1773128</t>
+          <t>1708389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3443386</t>
+          <t>3402625</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2907918</t>
+          <t>3349782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3650099</t>
+          <t>3465180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>351353</t>
+          <t>397166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239341</t>
+          <t>358027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>411908</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>535030</t>
+          <t>375873</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>351112</t>
+          <t>344400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>992212</t>
+          <t>413347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>886383</t>
+          <t>773039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>677798</t>
+          <t>717239</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1430700</t>
+          <t>828285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>101293</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63168</t>
+          <t>82910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115729</t>
+          <t>126464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>106703</t>
+          <t>124080</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75790</t>
+          <t>104105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133024</t>
+          <t>147670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>197524</t>
+          <t>225374</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157656</t>
+          <t>198890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236173</t>
+          <t>259584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2236966</t>
+          <t>2170471</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2236966</t>
+          <t>2170471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2236966</t>
+          <t>2170471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4527293</t>
+          <t>4401037</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4527293</t>
+          <t>4401037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4527293</t>
+          <t>4401037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>466942</t>
+          <t>518658</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>439032</t>
+          <t>492340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>492753</t>
+          <t>542725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>484884</t>
+          <t>537460</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>463515</t>
+          <t>515074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>504137</t>
+          <t>557046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>951826</t>
+          <t>1056118</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>912847</t>
+          <t>1020484</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>983723</t>
+          <t>1089070</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>138280</t>
+          <t>154449</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115392</t>
+          <t>131576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159449</t>
+          <t>179232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125437</t>
+          <t>139391</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108675</t>
+          <t>120095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144271</t>
+          <t>158643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>263717</t>
+          <t>293839</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237672</t>
+          <t>264548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294635</t>
+          <t>328117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71300</t>
+          <t>52616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48801</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38097</t>
+          <t>45609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62605</t>
+          <t>70235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>90202</t>
+          <t>95076</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70831</t>
+          <t>78596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120756</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2720516</t>
+          <t>2705209</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2642690</t>
+          <t>2651106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2888729</t>
+          <t>2761645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2676863</t>
+          <t>2853199</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2159823</t>
+          <t>2806034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2855658</t>
+          <t>2901206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5397380</t>
+          <t>5558408</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4819595</t>
+          <t>5483280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5592956</t>
+          <t>5631850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>559225</t>
+          <t>633378</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434909</t>
+          <t>576995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623305</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>772736</t>
+          <t>640719</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>584445</t>
+          <t>595622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1334282</t>
+          <t>682103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1331960</t>
+          <t>1274097</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129633</t>
+          <t>1206363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1938707</t>
+          <t>1341453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>170294</t>
+          <t>180165</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130097</t>
+          <t>154861</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>210330</t>
+          <t>211444</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>201375</t>
+          <t>231362</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>163252</t>
+          <t>205124</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232468</t>
+          <t>261114</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>371669</t>
+          <t>411526</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>317751</t>
+          <t>374109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>420189</t>
+          <t>453828</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3450035</t>
+          <t>3518752</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3450035</t>
+          <t>3518752</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3450035</t>
+          <t>3518752</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3650974</t>
+          <t>3725280</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3650974</t>
+          <t>3725280</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3650974</t>
+          <t>3725280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7101009</t>
+          <t>7244031</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7101009</t>
+          <t>7244031</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7101009</t>
+          <t>7244031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
